--- a/Result/profitability/4133.xlsx
+++ b/Result/profitability/4133.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM73"/>
+  <dimension ref="A1:AM74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.33</v>
       </c>
       <c r="M2" t="n">
-        <v>0.10625</v>
+        <v>0.1125</v>
       </c>
       <c r="N2" t="n">
-        <v>48.69499999999999</v>
+        <v>49.36</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.29</v>
       </c>
       <c r="M3" t="n">
-        <v>0.13625</v>
+        <v>0.12125</v>
       </c>
       <c r="N3" t="n">
-        <v>51.0925</v>
+        <v>52.06</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,13 +899,13 @@
         <v>0.11</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1225</v>
+        <v>0.1075</v>
       </c>
       <c r="N4" t="n">
-        <v>53.30625</v>
+        <v>54.22375</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.46</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1525</v>
+        <v>0.24125</v>
       </c>
       <c r="N5" t="n">
-        <v>55.24625</v>
+        <v>56.24</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>98.09999999999999</v>
@@ -1137,10 +1137,10 @@
         <v>0.61</v>
       </c>
       <c r="M6" t="n">
-        <v>0.305</v>
+        <v>0.29375</v>
       </c>
       <c r="N6" t="n">
-        <v>56.54875</v>
+        <v>57.53875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.36</v>
       </c>
       <c r="M7" t="n">
-        <v>0.32625</v>
+        <v>0.3175</v>
       </c>
       <c r="N7" t="n">
-        <v>57.9025</v>
+        <v>58.48375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.41</v>
       </c>
       <c r="M8" t="n">
-        <v>0.35625</v>
+        <v>0.33375</v>
       </c>
       <c r="N8" t="n">
-        <v>59.7625</v>
+        <v>59.61875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9699,6 +9699,133 @@
       </c>
       <c r="AM73" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>4133</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>88</v>
+      </c>
+      <c r="D74" t="n">
+        <v>43</v>
+      </c>
+      <c r="E74" t="n">
+        <v>45</v>
+      </c>
+      <c r="F74" t="n">
+        <v>51.35</v>
+      </c>
+      <c r="G74" t="n">
+        <v>7</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>8.06%</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" t="n">
+        <v>8</v>
+      </c>
+      <c r="K74" t="n">
+        <v>6</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.0775</v>
+      </c>
+      <c r="N74" t="n">
+        <v>46.37875</v>
+      </c>
+      <c r="O74" t="n">
+        <v>1</v>
+      </c>
+      <c r="P74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W74" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="X74" t="n">
+        <v>-0.6428571428571428</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>-1.149999999999999</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>-0.02190476190476187</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>-1.163934426229508</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>7.950000000000003</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>0.1831797235023043</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK74" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
